--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 15,75</t>
+          <t>8,99; 15,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 16,07</t>
+          <t>9,25; 15,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 16,42</t>
+          <t>10,3; 16,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 16,54</t>
+          <t>8,47; 16,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 17,8</t>
+          <t>9,89; 18,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,95</t>
+          <t>20,21; 26,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,79</t>
+          <t>9,7; 14,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,68</t>
+          <t>10,59; 15,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,3</t>
+          <t>15,86; 20,1</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 17,59</t>
+          <t>9,83; 17,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,82</t>
+          <t>8,6; 15,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,22; 18,46</t>
+          <t>12,32; 18,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,01; 23,85</t>
+          <t>14,56; 23,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 18,8</t>
+          <t>11,16; 18,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 30,52</t>
+          <t>23,3; 30,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 18,92</t>
+          <t>13,15; 18,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 15,74</t>
+          <t>10,74; 15,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,23; 23,32</t>
+          <t>18,13; 23,11</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,04; 26,26</t>
+          <t>19,19; 25,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 19,26</t>
+          <t>13,06; 19,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 20,09</t>
+          <t>4,52; 20,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,27; 34,91</t>
+          <t>23,34; 34,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,84; 39,55</t>
+          <t>24,73; 39,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,6; 46,28</t>
+          <t>33,3; 45,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,5; 27,54</t>
+          <t>20,87; 27,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 23,21</t>
+          <t>17,04; 23,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 25,79</t>
+          <t>8,34; 25,44</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,49; 22,44</t>
+          <t>17,35; 22,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,53; 18,74</t>
+          <t>14,5; 18,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 25,27</t>
+          <t>19,61; 24,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 24,18</t>
+          <t>17,8; 23,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,7; 22,41</t>
+          <t>16,73; 22,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 29,63</t>
+          <t>12,79; 29,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,14; 22,07</t>
+          <t>18,29; 22,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,13; 19,47</t>
+          <t>16,06; 19,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,01; 25,59</t>
+          <t>15,33; 25,43</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,95</t>
+          <t>15,46; 22,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,36; 23,75</t>
+          <t>17,26; 23,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 28,16</t>
+          <t>19,96; 27,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,23; 40,6</t>
+          <t>33,67; 40,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,41; 37,6</t>
+          <t>30,39; 37,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,03; 41,64</t>
+          <t>28,01; 42,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,92; 32,04</t>
+          <t>27,03; 32,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,38; 30,3</t>
+          <t>25,27; 30,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,44; 35,23</t>
+          <t>26,15; 35,03</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,51</t>
+          <t>1,17; 7,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,19</t>
+          <t>1,34; 5,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 18,37</t>
+          <t>5,34; 17,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,83; 40,73</t>
+          <t>34,84; 40,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,24; 34,22</t>
+          <t>28,17; 34,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,43</t>
+          <t>33,49; 39,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,62; 33,83</t>
+          <t>28,42; 33,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,9; 27,82</t>
+          <t>22,79; 27,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,99; 32,68</t>
+          <t>27,18; 33,22</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,62; 18,36</t>
+          <t>15,63; 18,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,79; 16,26</t>
+          <t>13,68; 16,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,18</t>
+          <t>13,57; 19,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,66; 30,65</t>
+          <t>27,65; 30,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,13; 27,24</t>
+          <t>23,98; 27,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,14; 32,7</t>
+          <t>24,32; 32,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,09; 24,19</t>
+          <t>22,1; 24,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,48; 21,49</t>
+          <t>19,42; 21,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,81</t>
+          <t>20,9; 25,6</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40059; 68851</t>
+          <t>39320; 68362</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40137; 68942</t>
+          <t>39675; 68297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52374; 82941</t>
+          <t>52061; 80944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27239; 52017</t>
+          <t>26643; 51564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35248; 61790</t>
+          <t>34317; 62537</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90813; 120587</t>
+          <t>90423; 120216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72290; 111179</t>
+          <t>72902; 108866</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82288; 121722</t>
+          <t>82173; 121192</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>150331; 193438</t>
+          <t>151096; 191472</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42961; 73658</t>
+          <t>41158; 72248</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33356; 59676</t>
+          <t>32455; 58235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55262; 83490</t>
+          <t>55730; 85479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50734; 80616</t>
+          <t>49228; 79831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40449; 69992</t>
+          <t>41539; 69756</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88282; 116762</t>
+          <t>89124; 117118</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>99707; 143211</t>
+          <t>99498; 143003</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80384; 117958</t>
+          <t>80513; 119854</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152192; 194677</t>
+          <t>151358; 192937</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>119842; 165294</t>
+          <t>120794; 162415</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69545; 100510</t>
+          <t>68160; 101561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29447; 134254</t>
+          <t>30223; 134258</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60533; 90808</t>
+          <t>60707; 90994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39607; 65695</t>
+          <t>41079; 66266</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56076; 77241</t>
+          <t>55575; 76286</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>191211; 244992</t>
+          <t>185668; 242533</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>116274; 159682</t>
+          <t>117258; 161189</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63146; 215422</t>
+          <t>69657; 212441</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>202727; 260073</t>
+          <t>201102; 258495</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167055; 215466</t>
+          <t>166651; 216250</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206964; 261505</t>
+          <t>202900; 254696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138044; 185396</t>
+          <t>136464; 182884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>137913; 185119</t>
+          <t>138198; 185134</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>113357; 289833</t>
+          <t>125087; 288952</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>349224; 425029</t>
+          <t>352140; 427048</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>318637; 384562</t>
+          <t>317271; 385326</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>322296; 515032</t>
+          <t>308550; 511873</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77847; 112096</t>
+          <t>78923; 112745</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107724; 147399</t>
+          <t>107115; 145046</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95895; 133776</t>
+          <t>94841; 132261</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>253045; 309143</t>
+          <t>256399; 307640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>224507; 277568</t>
+          <t>224322; 277867</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>219040; 350300</t>
+          <t>235666; 355109</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>342418; 407647</t>
+          <t>343847; 412687</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>344860; 411761</t>
+          <t>343352; 409663</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>348098; 463818</t>
+          <t>344205; 461105</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3084; 17362</t>
+          <t>3120; 18717</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3913; 14913</t>
+          <t>3847; 15860</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12722; 44187</t>
+          <t>12833; 41194</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>386413; 451880</t>
+          <t>386539; 452488</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>305575; 370261</t>
+          <t>304763; 370353</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>251996; 300205</t>
+          <t>254984; 302068</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>393833; 465647</t>
+          <t>391107; 464124</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>313586; 380894</t>
+          <t>312072; 380024</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>270406; 327369</t>
+          <t>272284; 332782</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>534346; 628361</t>
+          <t>534943; 622457</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>466936; 550393</t>
+          <t>463019; 546206</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>441164; 647362</t>
+          <t>457994; 649457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>981902; 1088258</t>
+          <t>981486; 1094456</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>852059; 961894</t>
+          <t>846782; 957768</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>863664; 1169995</t>
+          <t>870021; 1167687</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1540170; 1686798</t>
+          <t>1540667; 1679235</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1347455; 1486860</t>
+          <t>1343435; 1483467</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1446583; 1794941</t>
+          <t>1453470; 1780080</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 15,64</t>
+          <t>8,86; 15,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 15,92</t>
+          <t>8,93; 15,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,3; 16,02</t>
+          <t>10,84; 16,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 16,4</t>
+          <t>8,47; 16,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,02</t>
+          <t>9,91; 17,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 26,87</t>
+          <t>20,24; 26,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,48</t>
+          <t>9,68; 14,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 15,61</t>
+          <t>10,5; 15,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 20,1</t>
+          <t>15,91; 20,45</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 17,25</t>
+          <t>10,12; 17,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 15,44</t>
+          <t>8,75; 15,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,32; 18,9</t>
+          <t>11,98; 17,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 23,62</t>
+          <t>15,03; 23,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 18,74</t>
+          <t>11,05; 18,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 30,61</t>
+          <t>24,36; 31,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 18,9</t>
+          <t>13,01; 19,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,99</t>
+          <t>10,75; 15,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 23,11</t>
+          <t>18,27; 23,55</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,19; 25,8</t>
+          <t>19,17; 26,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 19,46</t>
+          <t>13,02; 19,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 20,09</t>
+          <t>14,84; 21,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,34; 34,98</t>
+          <t>23,41; 35,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,73; 39,89</t>
+          <t>24,47; 40,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,3; 45,7</t>
+          <t>33,26; 45,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,87; 27,26</t>
+          <t>21,38; 27,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 23,43</t>
+          <t>16,67; 23,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 25,44</t>
+          <t>21,24; 27,31</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,35; 22,3</t>
+          <t>17,34; 22,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,5; 18,81</t>
+          <t>14,42; 18,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,61</t>
+          <t>19,65; 24,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 23,85</t>
+          <t>18,07; 24,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 22,42</t>
+          <t>17,03; 22,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 29,54</t>
+          <t>26,44; 31,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 22,18</t>
+          <t>18,34; 22,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 19,51</t>
+          <t>16,09; 19,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 25,43</t>
+          <t>23,21; 26,65</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,46; 22,08</t>
+          <t>14,84; 21,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,26; 23,37</t>
+          <t>17,27; 23,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,96; 27,84</t>
+          <t>18,03; 25,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,67; 40,4</t>
+          <t>33,3; 40,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,39; 37,64</t>
+          <t>30,48; 37,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,01; 42,21</t>
+          <t>37,08; 42,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 32,44</t>
+          <t>27,1; 32,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,27; 30,15</t>
+          <t>25,18; 30,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,15; 35,03</t>
+          <t>30,12; 34,63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,01</t>
+          <t>1,14; 6,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,52</t>
+          <t>1,38; 5,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 17,13</t>
+          <t>5,68; 18,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,84; 40,79</t>
+          <t>34,79; 40,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,17; 34,23</t>
+          <t>28,43; 34,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,49; 39,67</t>
+          <t>32,59; 39,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,42; 33,72</t>
+          <t>28,27; 33,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,79; 27,76</t>
+          <t>22,9; 27,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,18; 33,22</t>
+          <t>27,19; 32,77</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,63; 18,19</t>
+          <t>15,67; 18,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,13</t>
+          <t>13,65; 16,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 19,24</t>
+          <t>16,91; 19,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,65; 30,83</t>
+          <t>27,66; 30,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,98; 27,12</t>
+          <t>24,05; 27,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,32; 32,64</t>
+          <t>31,21; 33,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,1; 24,09</t>
+          <t>22,28; 24,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,42; 21,45</t>
+          <t>19,46; 21,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,9; 25,6</t>
+          <t>24,66; 26,55</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66359</t>
+          <t>73878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>104487</t>
+          <t>114492</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>170846</t>
+          <t>188370</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39320; 68362</t>
+          <t>38754; 67749</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39675; 68297</t>
+          <t>38328; 66783</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52061; 80944</t>
+          <t>59697; 90321</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26643; 51564</t>
+          <t>26637; 50738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34317; 62537</t>
+          <t>34410; 61658</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90423; 120216</t>
+          <t>98837; 129819</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72902; 108866</t>
+          <t>72768; 109122</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82173; 121192</t>
+          <t>81475; 119910</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>151096; 191472</t>
+          <t>165269; 212506</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>71967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>102667</t>
+          <t>116605</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>172214</t>
+          <t>188571</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41158; 72248</t>
+          <t>42398; 74451</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32455; 58235</t>
+          <t>33015; 59586</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55730; 85479</t>
+          <t>57889; 86774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49228; 79831</t>
+          <t>50816; 80786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41539; 69756</t>
+          <t>41151; 70266</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89124; 117118</t>
+          <t>103059; 132020</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>99498; 143003</t>
+          <t>98477; 143782</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80513; 119854</t>
+          <t>80600; 118536</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>151358; 192937</t>
+          <t>165609; 213446</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80312</t>
+          <t>85708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65829</t>
+          <t>72605</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146141</t>
+          <t>158313</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>120794; 162415</t>
+          <t>120663; 165255</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68160; 101561</t>
+          <t>67969; 102022</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30223; 134258</t>
+          <t>69972; 101714</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60707; 90994</t>
+          <t>60884; 91067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41079; 66266</t>
+          <t>40649; 66721</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55575; 76286</t>
+          <t>62362; 85296</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>185668; 242533</t>
+          <t>190189; 243000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>117258; 161189</t>
+          <t>114718; 159474</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69657; 212441</t>
+          <t>140023; 179994</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230186</t>
+          <t>249865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>221085</t>
+          <t>249032</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>451271</t>
+          <t>498897</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>201102; 258495</t>
+          <t>200981; 256411</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>166651; 216250</t>
+          <t>165781; 218135</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>202900; 254696</t>
+          <t>222430; 280802</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136464; 182884</t>
+          <t>138534; 184037</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>138198; 185134</t>
+          <t>140611; 188226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>125087; 288952</t>
+          <t>227725; 271294</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>352140; 427048</t>
+          <t>353184; 426599</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>317271; 385326</t>
+          <t>317919; 388163</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>308550; 511873</t>
+          <t>462653; 531216</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>121924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>306160</t>
+          <t>330419</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>419263</t>
+          <t>452343</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>78923; 112745</t>
+          <t>75758; 111802</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107115; 145046</t>
+          <t>107199; 146923</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94841; 132261</t>
+          <t>102401; 142401</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>256399; 307640</t>
+          <t>253604; 308026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>224322; 277867</t>
+          <t>225008; 278018</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>235666; 355109</t>
+          <t>308093; 355258</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>343847; 412687</t>
+          <t>344757; 409609</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>343352; 409663</t>
+          <t>342148; 411141</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>344205; 461105</t>
+          <t>421261; 484351</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>276317</t>
+          <t>301311</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>299820</t>
+          <t>324579</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3120; 18717</t>
+          <t>3049; 17354</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3847; 15860</t>
+          <t>3959; 15430</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12833; 41194</t>
+          <t>13477; 42935</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>386539; 452488</t>
+          <t>385950; 453143</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>304763; 370353</t>
+          <t>307612; 369190</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>254984; 302068</t>
+          <t>275179; 329383</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>391107; 464124</t>
+          <t>389122; 461439</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>312072; 380024</t>
+          <t>313585; 381387</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>272284; 332782</t>
+          <t>294025; 354380</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>583011</t>
+          <t>626610</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1076544</t>
+          <t>1184464</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1659555</t>
+          <t>1811074</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>534943; 622457</t>
+          <t>536318; 626756</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>463019; 546206</t>
+          <t>462062; 546704</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>457994; 649457</t>
+          <t>582104; 676260</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>981486; 1094456</t>
+          <t>981920; 1094401</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>846782; 957768</t>
+          <t>849497; 960735</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>870021; 1167687</t>
+          <t>1134623; 1231469</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1540667; 1679235</t>
+          <t>1553592; 1693010</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1343435; 1483467</t>
+          <t>1345792; 1484032</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1453470; 1780080</t>
+          <t>1745243; 1878886</t>
         </is>
       </c>
     </row>
